--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事项明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="事项明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -526,17 +526,22 @@
           <t>LIVOX对接人</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>进展</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>提交物链接</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>闭环状态</t>
         </is>
@@ -568,17 +573,22 @@
           <t>如：Dandy</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>高/中/低，留空默认中</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>当前进展说明</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://... 或留空</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>未完成 / 完成 / 挂起</t>
         </is>
@@ -610,17 +620,22 @@
           <t>Dandy</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>初次已经提交</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>https://www.kdocs.cn/l/chcPb0L1SJnl</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
@@ -652,13 +667,18 @@
           <t>Dandy/卓玟</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>客户邀约进行中</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -690,13 +710,18 @@
           <t>Dandy</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>7月20日已完成</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>完成</t>
         </is>

--- a/template.xlsx
+++ b/template.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -531,17 +531,27 @@
           <t>优先级</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>重复性待办</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>周期说明</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>进展</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>提交物链接</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>闭环状态</t>
         </is>
@@ -560,7 +570,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>如：2026-08-15 或 每月更新</t>
+          <t>如：2026-08-15（一次性截止日 / 重复性待办下次到期日，均需真实日期）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -578,17 +588,27 @@
           <t>高/中/低，留空默认中</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>是/否，留空默认否</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>如：每月31日，仅重复性待办填写</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>当前进展说明</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>https://... 或留空</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>未完成 / 完成 / 挂起</t>
         </is>
@@ -607,7 +627,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>每月更新</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -625,17 +645,27 @@
           <t>中</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>每月31日</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>初次已经提交</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>https://www.kdocs.cn/l/chcPb0L1SJnl</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
@@ -672,13 +702,18 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>客户邀约进行中</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -697,31 +732,41 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>杨朔&amp;李建萍</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Dandy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>每月更新</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>杨朔&amp;李建萍</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Dandy</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>7月20日已完成</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>完成</t>
         </is>

--- a/template.xlsx
+++ b/template.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -521,37 +521,42 @@
           <t>责任人</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>发起人</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LIVOX对接人</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>重复性待办</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>周期说明</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>进展</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>提交物链接</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>闭环状态</t>
         </is>
@@ -578,37 +583,42 @@
           <t>如：赵云飞 或 赵云飞&amp;李建萍</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>任务发起人，如：Dandy</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>如：Dandy</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>高/中/低，留空默认中</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>是/否，留空默认否</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>如：每月31日，仅重复性待办填写</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>当前进展说明</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>https://... 或留空</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>未完成 / 完成 / 挂起</t>
         </is>
@@ -635,37 +645,42 @@
           <t>赵云飞</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Dandy</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Dandy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>每月31日</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>初次已经提交</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>https://www.kdocs.cn/l/chcPb0L1SJnl</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
@@ -692,28 +707,33 @@
           <t>杨海月</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dandy</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Dandy/卓玟</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>客户邀约进行中</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -740,33 +760,38 @@
           <t>杨朔&amp;李建萍</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Dandy</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Dandy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>每月更新</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>7月20日已完成</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
